--- a/input/sample.xlsx
+++ b/input/sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\fjmr5125\dev\ruby\flr2dat\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776686DC-A2D7-46AC-92B9-E788E70BDA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D49092-E305-4C55-B36E-F2642AA1B69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="1155" windowWidth="17408" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="def" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="30">
   <si>
     <t>byte</t>
     <phoneticPr fontId="1"/>
@@ -203,6 +203,10 @@
     <rPh sb="3" eb="5">
       <t>セイメイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>$space</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -243,18 +247,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -285,11 +283,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -584,33 +582,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="5" customFormat="1">
+    <row r="2" spans="1:5" s="4" customFormat="1">
       <c r="A2"/>
       <c r="B2"/>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <f>MAX(C4:XFD4)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="5" customFormat="1">
+    <row r="3" spans="1:5" s="4" customFormat="1">
       <c r="A3"/>
       <c r="B3"/>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="5" customFormat="1">
+    <row r="4" spans="1:5" s="4" customFormat="1">
       <c r="A4"/>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
         <v>3</v>
       </c>
     </row>
@@ -645,8 +643,12 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="B1">
-        <f>COUNTA(B5:B1048576)</f>
-        <v>1</v>
+        <f>COUNTA(C5:C1048576)</f>
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <f>COUNTA(C4:XFD4)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" ht="18">
@@ -801,23 +803,14 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1">
-        <f>LENB(B5)</f>
-        <v>100</v>
-      </c>
-      <c r="B5" t="str">
-        <f>_xlfn.TEXTJOIN("",TRUE,C5:XFD5)</f>
-        <v xml:space="preserve">21 12345678900225250704                       3312345678900821                                      </v>
-      </c>
       <c r="C5" s="2">
         <v>2</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <f>REPT(" ",E$3)</f>
-        <v xml:space="preserve"> </v>
+      <c r="E5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="F5" s="2">
         <v>1234567890</v>
@@ -831,9 +824,8 @@
       <c r="I5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="3" t="str">
-        <f>REPT(" ",J$3)</f>
-        <v xml:space="preserve">                       </v>
+      <c r="J5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>18</v>
@@ -850,13 +842,11 @@
       <c r="O5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="3" t="str">
-        <f t="shared" ref="P5:Q5" si="0">REPT(" ",P$3)</f>
-        <v xml:space="preserve">                    </v>
-      </c>
-      <c r="Q5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">                  </v>
+      <c r="P5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -876,8 +866,12 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="B1">
-        <f>COUNTA(B5:B1048576)</f>
-        <v>1</v>
+        <f>COUNTA(C5:C1048576)</f>
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <f>COUNTA(C4:XFD4)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" ht="18">
@@ -1032,23 +1026,14 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1">
-        <f>LENB(B5)</f>
-        <v>100</v>
-      </c>
-      <c r="B5" t="str">
-        <f>_xlfn.TEXTJOIN("",TRUE,C5:XFD5)</f>
-        <v xml:space="preserve">21 12345678900225250704                       3312345678900821                                      </v>
-      </c>
       <c r="C5" s="2">
         <v>2</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <f>REPT(" ",E$3)</f>
-        <v xml:space="preserve"> </v>
+      <c r="E5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="F5" s="2">
         <v>1234567890</v>
@@ -1062,9 +1047,8 @@
       <c r="I5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="3" t="str">
-        <f>REPT(" ",J$3)</f>
-        <v xml:space="preserve">                       </v>
+      <c r="J5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>18</v>
@@ -1081,13 +1065,11 @@
       <c r="O5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="3" t="str">
-        <f t="shared" ref="P5:Q5" si="0">REPT(" ",P$3)</f>
-        <v xml:space="preserve">                    </v>
-      </c>
-      <c r="Q5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">                  </v>
+      <c r="P5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1107,8 +1089,12 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="B1">
-        <f>COUNTA(B5:B1048576)</f>
-        <v>1</v>
+        <f>COUNTA(C5:C1048576)</f>
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <f>COUNTA(C4:XFD4)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="1" customFormat="1" ht="18">
@@ -1263,23 +1249,14 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1">
-        <f>LENB(B5)</f>
-        <v>100</v>
-      </c>
-      <c r="B5" t="str">
-        <f>_xlfn.TEXTJOIN("",TRUE,C5:XFD5)</f>
-        <v xml:space="preserve">21 12345678900225250704                       3312345678900821                                      </v>
-      </c>
       <c r="C5" s="2">
         <v>2</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <f>REPT(" ",E$3)</f>
-        <v xml:space="preserve"> </v>
+      <c r="E5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="F5" s="2">
         <v>1234567890</v>
@@ -1293,9 +1270,8 @@
       <c r="I5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="3" t="str">
-        <f>REPT(" ",J$3)</f>
-        <v xml:space="preserve">                       </v>
+      <c r="J5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>18</v>
@@ -1312,13 +1288,11 @@
       <c r="O5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="3" t="str">
-        <f t="shared" ref="P5:Q5" si="0">REPT(" ",P$3)</f>
-        <v xml:space="preserve">                    </v>
-      </c>
-      <c r="Q5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">                  </v>
+      <c r="P5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
